--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.08385647677042</v>
+        <v>8.138626677475195</v>
       </c>
       <c r="D2" t="n">
-        <v>8.889462890747255</v>
+        <v>1.444537719746429</v>
       </c>
       <c r="E2" t="n">
-        <v>13.70146231640384</v>
+        <v>2.226487626415625</v>
       </c>
       <c r="F2" t="n">
-        <v>13.03829348812366</v>
+        <v>2.118722691820095</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.96305266440684</v>
+        <v>3.081496057966111</v>
       </c>
       <c r="D3" t="n">
-        <v>22.92507043917723</v>
+        <v>3.725323946366299</v>
       </c>
       <c r="E3" t="n">
-        <v>13.70146231640384</v>
+        <v>2.226487626415625</v>
       </c>
       <c r="F3" t="n">
-        <v>13.03829348812366</v>
+        <v>2.118722691820095</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.54799135306245</v>
+        <v>6.264048594872649</v>
       </c>
       <c r="D4" t="n">
-        <v>39.62977121936702</v>
+        <v>6.439837823147141</v>
       </c>
       <c r="E4" t="n">
-        <v>13.70146231640384</v>
+        <v>2.226487626415625</v>
       </c>
       <c r="F4" t="n">
-        <v>13.03829348812366</v>
+        <v>2.118722691820095</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.7325474865163</v>
+        <v>2.069038966558899</v>
       </c>
       <c r="D5" t="n">
-        <v>11.2875789052509</v>
+        <v>1.834231572103272</v>
       </c>
       <c r="E5" t="n">
-        <v>13.70146231640384</v>
+        <v>2.226487626415625</v>
       </c>
       <c r="F5" t="n">
-        <v>13.03829348812366</v>
+        <v>2.118722691820095</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.11673846105999</v>
+        <v>2.618969999922248</v>
       </c>
       <c r="D6" t="n">
-        <v>17.23461118913147</v>
+        <v>2.800624318233864</v>
       </c>
       <c r="E6" t="n">
-        <v>13.70146231640384</v>
+        <v>2.226487626415625</v>
       </c>
       <c r="F6" t="n">
-        <v>13.03829348812366</v>
+        <v>2.118722691820095</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.07358745167586</v>
+        <v>6.024457960897327</v>
       </c>
       <c r="D7" t="n">
-        <v>37.56227429895569</v>
+        <v>6.1038695735803</v>
       </c>
       <c r="E7" t="n">
-        <v>13.70146231640384</v>
+        <v>2.226487626415625</v>
       </c>
       <c r="F7" t="n">
-        <v>13.03829348812366</v>
+        <v>2.118722691820095</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.38895534536008</v>
+        <v>3.313205243621014</v>
       </c>
       <c r="D8" t="n">
-        <v>3.928985762859709</v>
+        <v>0.6384601864647027</v>
       </c>
       <c r="E8" t="n">
-        <v>13.70146231640384</v>
+        <v>2.226487626415625</v>
       </c>
       <c r="F8" t="n">
-        <v>13.03829348812366</v>
+        <v>2.118722691820095</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>29.41436665005338</v>
+        <v>4.779834580633675</v>
       </c>
       <c r="D9" t="n">
-        <v>25.81059131349402</v>
+        <v>4.194221088442777</v>
       </c>
       <c r="E9" t="n">
-        <v>13.70146231640384</v>
+        <v>2.226487626415625</v>
       </c>
       <c r="F9" t="n">
-        <v>13.03829348812366</v>
+        <v>2.118722691820095</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>15.8304820697798</v>
+        <v>2.572453336339219</v>
       </c>
       <c r="D10" t="n">
-        <v>14.71442811438563</v>
+        <v>2.391094568587664</v>
       </c>
       <c r="E10" t="n">
-        <v>13.70146231640384</v>
+        <v>2.226487626415625</v>
       </c>
       <c r="F10" t="n">
-        <v>13.03829348812366</v>
+        <v>2.118722691820095</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>51.30108710887652</v>
+        <v>8.336426655192435</v>
       </c>
       <c r="D11" t="n">
-        <v>43.09957898355955</v>
+        <v>7.003681584828427</v>
       </c>
       <c r="E11" t="n">
-        <v>13.70146231640384</v>
+        <v>2.226487626415625</v>
       </c>
       <c r="F11" t="n">
-        <v>13.03829348812366</v>
+        <v>2.118722691820095</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
